--- a/GRAMMAR/5_20_12.xlsx
+++ b/GRAMMAR/5_20_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C0A034-9522-4B39-8280-8B4D1B35DB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048AE9EA-F496-4575-908F-D8D414863F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="3000" windowWidth="23580" windowHeight="17835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,278 +39,277 @@
     <t>备注</t>
   </si>
   <si>
+    <t>楽しむ</t>
+  </si>
+  <si>
+    <t>享受</t>
+  </si>
+  <si>
+    <t>たのしむ</t>
+  </si>
+  <si>
+    <t>たっけ</t>
+  </si>
+  <si>
+    <t>（回忆）...来着？</t>
+  </si>
+  <si>
+    <t>Vる+つもり</t>
+  </si>
+  <si>
+    <t>打算...</t>
+  </si>
+  <si>
+    <t>にすぎない</t>
+  </si>
+  <si>
+    <t>只不过是...</t>
+  </si>
+  <si>
+    <t>ざるを得ない</t>
+  </si>
+  <si>
+    <t>不得不...</t>
+  </si>
+  <si>
+    <t>ざるをえない</t>
+  </si>
+  <si>
+    <t>本物そっくりに</t>
+  </si>
+  <si>
+    <t>和真的一模一样地</t>
+  </si>
+  <si>
+    <t>ほんものそっくりに</t>
+  </si>
+  <si>
+    <t>たがる</t>
+  </si>
+  <si>
+    <t>（第三方）想要...</t>
+  </si>
+  <si>
+    <t>ようこそ</t>
+  </si>
+  <si>
+    <t>欢迎</t>
+  </si>
+  <si>
+    <t>なんて</t>
+  </si>
+  <si>
+    <t>...之类的（表轻视或惊讶）</t>
+  </si>
+  <si>
+    <t>“なんて～だろう”多么…啊</t>
+  </si>
+  <si>
+    <t>分野</t>
+  </si>
+  <si>
+    <t>领域，范围</t>
+  </si>
+  <si>
+    <t>ぶんや</t>
+  </si>
+  <si>
+    <t>時間+ぶりに</t>
+  </si>
+  <si>
+    <t>隔了...时间后</t>
+  </si>
+  <si>
+    <t>じかん+ぶりに</t>
+  </si>
+  <si>
+    <t>介護</t>
+  </si>
+  <si>
+    <t>护理，照顾</t>
+  </si>
+  <si>
+    <t>かいご</t>
+  </si>
+  <si>
+    <t>たことのある</t>
+  </si>
+  <si>
+    <t>有过...经验的</t>
+  </si>
+  <si>
+    <t>触れ合う</t>
+  </si>
+  <si>
+    <t>互相接触，心灵相通</t>
+  </si>
+  <si>
+    <t>ふれあう</t>
+  </si>
+  <si>
+    <t>ことで</t>
+  </si>
+  <si>
+    <t>通过...，因为...</t>
+  </si>
+  <si>
+    <t>(V)おうとする</t>
+  </si>
+  <si>
+    <t>想要/试图做...</t>
+  </si>
+  <si>
+    <t>ご存じでしょうか</t>
+  </si>
+  <si>
+    <t>您知道吗？（敬语）</t>
+  </si>
+  <si>
+    <t>ごぞんじでしょうか</t>
+  </si>
+  <si>
+    <t>てもかまいません</t>
+  </si>
+  <si>
+    <t>...也没关系</t>
+  </si>
+  <si>
+    <t>てばかり</t>
+  </si>
+  <si>
+    <t>净是...，光是...</t>
+  </si>
+  <si>
+    <t>“たばかり”刚…</t>
+  </si>
+  <si>
+    <t>〜てしまう</t>
+  </si>
+  <si>
+    <t>（动作）完成；（表示遗憾）</t>
+  </si>
+  <si>
+    <t>ないか</t>
+  </si>
+  <si>
+    <t>是不是怎么….样</t>
+  </si>
+  <si>
+    <t>“否定+か”不再是否定，而是不确定的推测</t>
+  </si>
+  <si>
+    <t>ほとんど</t>
+  </si>
+  <si>
+    <t>几乎，大部分</t>
+  </si>
+  <si>
+    <t>うちに</t>
+  </si>
+  <si>
+    <t>在...期间；趁着...</t>
+  </si>
+  <si>
+    <t>エビ</t>
+  </si>
+  <si>
+    <t>虾</t>
+  </si>
+  <si>
+    <t>ものを</t>
+  </si>
+  <si>
+    <t>明明...却...（表不满、遗憾）</t>
+  </si>
+  <si>
+    <t>ところから</t>
+  </si>
+  <si>
+    <t>因为</t>
+  </si>
+  <si>
+    <t>同“ことから”“ことで”</t>
+  </si>
+  <si>
+    <t>N+のうえで(は)</t>
+  </si>
+  <si>
+    <t>根据…来看</t>
+  </si>
+  <si>
+    <t>だけです</t>
+  </si>
+  <si>
+    <t>只是...而已</t>
+  </si>
+  <si>
+    <t>少しも + 否定</t>
+  </si>
+  <si>
+    <t>一点也（不）...</t>
+  </si>
+  <si>
+    <t>すこしも + ひてい</t>
+  </si>
+  <si>
+    <t>場合には</t>
+  </si>
+  <si>
+    <t>在...的情况下</t>
+  </si>
+  <si>
+    <t>ばあいには</t>
+  </si>
+  <si>
+    <t>点には</t>
+  </si>
+  <si>
+    <t>在...这一点上</t>
+  </si>
+  <si>
+    <t>てんには</t>
+  </si>
+  <si>
+    <t>けっこう</t>
+  </si>
+  <si>
+    <t>相当，很；足够</t>
+  </si>
+  <si>
+    <t>よう+である</t>
+  </si>
+  <si>
+    <t>同“です”</t>
+  </si>
+  <si>
+    <t>Ｖる+うえで</t>
+  </si>
+  <si>
+    <t>在…方面，在…时</t>
+  </si>
+  <si>
+    <t>Ｖた＋うえで</t>
+  </si>
+  <si>
+    <t>在…之后，在…基础上</t>
+  </si>
+  <si>
+    <t>よう</t>
+  </si>
+  <si>
+    <t>(1)主观推测(2)比喻(3)示例</t>
+  </si>
+  <si>
+    <t>らしく</t>
+  </si>
+  <si>
+    <t>らしい的中顿，而不是“らしくて”</t>
+  </si>
+  <si>
     <t>〜ようでいて</t>
   </si>
   <si>
     <t>看起来像是...但实际上...</t>
-  </si>
-  <si>
-    <t>N+のうえで(は)</t>
-  </si>
-  <si>
-    <t>根据…来看</t>
-  </si>
-  <si>
-    <t>たっけ</t>
-  </si>
-  <si>
-    <t>（回忆）...来着？</t>
-  </si>
-  <si>
-    <t>よう+である</t>
-  </si>
-  <si>
-    <t>同“です”</t>
-  </si>
-  <si>
-    <t>Ｖた＋うえで</t>
-  </si>
-  <si>
-    <t>在…之后，在…基础上</t>
-  </si>
-  <si>
-    <t>Ｖる+うえで</t>
-  </si>
-  <si>
-    <t>在…方面，在…时</t>
-  </si>
-  <si>
-    <t>几乎，大部分</t>
-  </si>
-  <si>
-    <t>ご存じでしょうか</t>
-  </si>
-  <si>
-    <t>您知道吗？（敬语）</t>
-  </si>
-  <si>
-    <t>ごぞんじでしょうか</t>
-  </si>
-  <si>
-    <t>(V)おうとする</t>
-  </si>
-  <si>
-    <t>想要/试图做...</t>
-  </si>
-  <si>
-    <t>本物そっくりに</t>
-  </si>
-  <si>
-    <t>和真的一模一样地</t>
-  </si>
-  <si>
-    <t>ほんものそっくりに</t>
-  </si>
-  <si>
-    <t>たことのある</t>
-  </si>
-  <si>
-    <t>有过...经验的</t>
-  </si>
-  <si>
-    <t>けっこう</t>
-  </si>
-  <si>
-    <t>相当，很；足够</t>
-  </si>
-  <si>
-    <t>なんて</t>
-  </si>
-  <si>
-    <t>...之类的（表轻视或惊讶）</t>
-  </si>
-  <si>
-    <t>“なんて～だろう”多么…啊</t>
-  </si>
-  <si>
-    <t>らしく</t>
-  </si>
-  <si>
-    <t>らしい的中顿，而不是“らしくて”</t>
-  </si>
-  <si>
-    <t>場合には</t>
-  </si>
-  <si>
-    <t>在...的情况下</t>
-  </si>
-  <si>
-    <t>ばあいには</t>
-  </si>
-  <si>
-    <t>たがる</t>
-  </si>
-  <si>
-    <t>（第三方）想要...</t>
-  </si>
-  <si>
-    <t>うちに</t>
-  </si>
-  <si>
-    <t>在...期间；趁着...</t>
-  </si>
-  <si>
-    <t>点には</t>
-  </si>
-  <si>
-    <t>在...这一点上</t>
-  </si>
-  <si>
-    <t>てんには</t>
-  </si>
-  <si>
-    <t>ないか</t>
-  </si>
-  <si>
-    <t>是不是怎么….样</t>
-  </si>
-  <si>
-    <t>“否定+か”不再是否定，而是不确定的推测</t>
-  </si>
-  <si>
-    <t>よう</t>
-  </si>
-  <si>
-    <t>(1)主观推测(2)比喻(3)示例</t>
-  </si>
-  <si>
-    <t>触れ合う</t>
-  </si>
-  <si>
-    <t>互相接触，心灵相通</t>
-  </si>
-  <si>
-    <t>ふれあう</t>
-  </si>
-  <si>
-    <t>てばかり</t>
-  </si>
-  <si>
-    <t>净是...，光是...</t>
-  </si>
-  <si>
-    <t>“たばかり”刚…</t>
-  </si>
-  <si>
-    <t>少しも + 否定</t>
-  </si>
-  <si>
-    <t>一点也（不）...</t>
-  </si>
-  <si>
-    <t>すこしも + ひてい</t>
-  </si>
-  <si>
-    <t>ものを</t>
-  </si>
-  <si>
-    <t>明明...却...（表不满、遗憾）</t>
-  </si>
-  <si>
-    <t>だけです</t>
-  </si>
-  <si>
-    <t>只是...而已</t>
-  </si>
-  <si>
-    <t>ところから</t>
-  </si>
-  <si>
-    <t>因为</t>
-  </si>
-  <si>
-    <t>同“ことから”“ことで”</t>
-  </si>
-  <si>
-    <t>楽しむ</t>
-  </si>
-  <si>
-    <t>享受</t>
-  </si>
-  <si>
-    <t>たのしむ</t>
-  </si>
-  <si>
-    <t>エビ</t>
-  </si>
-  <si>
-    <t>虾</t>
-  </si>
-  <si>
-    <t>てもかまいません</t>
-  </si>
-  <si>
-    <t>...也没关系</t>
-  </si>
-  <si>
-    <t>にすぎない</t>
-  </si>
-  <si>
-    <t>只不过是...</t>
-  </si>
-  <si>
-    <t>介護</t>
-  </si>
-  <si>
-    <t>护理，照顾</t>
-  </si>
-  <si>
-    <t>かいご</t>
-  </si>
-  <si>
-    <t>時間+ぶりに</t>
-  </si>
-  <si>
-    <t>隔了...时间后</t>
-  </si>
-  <si>
-    <t>じかん+ぶりに</t>
-  </si>
-  <si>
-    <t>分野</t>
-  </si>
-  <si>
-    <t>领域，范围</t>
-  </si>
-  <si>
-    <t>ぶんや</t>
-  </si>
-  <si>
-    <t>ようこそ</t>
-  </si>
-  <si>
-    <t>欢迎</t>
-  </si>
-  <si>
-    <t>ざるを得ない</t>
-  </si>
-  <si>
-    <t>不得不...</t>
-  </si>
-  <si>
-    <t>ざるをえない</t>
-  </si>
-  <si>
-    <t>Vる+つもり</t>
-  </si>
-  <si>
-    <t>打算...</t>
-  </si>
-  <si>
-    <t>ことで</t>
-  </si>
-  <si>
-    <t>通过...，因为...</t>
-  </si>
-  <si>
-    <t>〜てしまう</t>
-  </si>
-  <si>
-    <t>（动作）完成；（表示遗憾）</t>
-  </si>
-  <si>
-    <t>ほとんど</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -710,7 +709,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -718,132 +717,147 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -851,13 +865,10 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
@@ -865,24 +876,24 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
@@ -890,10 +901,10 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
@@ -901,49 +912,49 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -951,27 +962,24 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -979,13 +987,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -993,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
@@ -1004,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
@@ -1015,27 +1020,24 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
@@ -1043,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -1054,121 +1056,118 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/GRAMMAR/5_20_12.xlsx
+++ b/GRAMMAR/5_20_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048AE9EA-F496-4575-908F-D8D414863F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DF4112-7FC5-47AE-8954-AE1DA4F67D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10560" yWindow="960" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
   <si>
     <t>Fre</t>
   </si>
@@ -306,17 +306,66 @@
     <t>らしい的中顿，而不是“らしくて”</t>
   </si>
   <si>
+    <t>看起来像是...但实际上...</t>
+  </si>
+  <si>
+    <t>没有不加否定的情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようこそ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欢迎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自谦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ご＋动词词干＋する</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なんて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竟然；竟然；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たっけ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（对于记不清的事进行确认）是…来着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よね</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…对吧？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お＋连用＋ました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>〜ようでいて</t>
-  </si>
-  <si>
-    <t>看起来像是...但实际上...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,13 +374,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -373,11 +432,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -680,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -708,470 +768,611 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E20" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="A22" s="2">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="A23" s="2">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>0</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E27" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="2">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29">
-        <v>0</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="E30" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="2">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A35">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A36">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A38">
-        <v>0</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A39">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>2</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>2</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>2</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>2</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="2">
+        <v>2</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1182,7 +1383,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1192,7 +1393,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GRAMMAR/5_20_12.xlsx
+++ b/GRAMMAR/5_20_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -483,33 +483,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>よね</t>
+          <t>点には</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>…对吧？</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>在...这一点上</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>てんには</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>お＋连用＋ました</t>
+          <t>N+のうえで(は)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>自谦</t>
+          <t>根据…来看</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -517,16 +521,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ようこそ</t>
+          <t>ほとんど</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>欢迎</t>
+          <t>几乎，大部分</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -534,28 +538,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>なんて</t>
+          <t>ないか</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(1)...之类的（表轻视或惊讶）(2)竟然</t>
+          <t>是不是怎么….样</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>“なんて～だろう”多么…啊</t>
+          <t>“否定+か”不再是否定，而是不确定的推测</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -564,7 +568,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>（对于记不清的事进行确认）是…来着</t>
+          <t>（回忆）...来着？</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -572,33 +576,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>たことのある</t>
+          <t>ご存じでしょうか</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>有过...经验的</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>您知道吗？（敬语）</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ごぞんじでしょうか</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N+のうえで(は)</t>
+          <t>(V)おうとする</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>根据…来看</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -606,50 +614,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ご＋动词词干＋する</t>
+          <t>場合には</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>自谦</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>在...的情况下</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ばあいには</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>よう</t>
+          <t>触れ合う</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(1)主观推测(2)比喻(3)示例</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>互相接触，心灵相通</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ふれあう</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>よう+である</t>
+          <t>たことのある</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>同“です”</t>
+          <t>有过...经验的</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -657,45 +673,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>触れ合う</t>
+          <t>けっこう</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>互相接触，心灵相通</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ふれあう</t>
-        </is>
-      </c>
+          <t>相当，很；足够</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ところから</t>
+          <t>よう+である</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>因为</t>
+          <t>同“です”</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>同“ことから”“ことで”</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -703,16 +711,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ほとんど</t>
+          <t>なんて</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>几乎，大部分</t>
+          <t>...之类的（表轻视或惊讶）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>“なんて～だろう”多么…啊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -720,20 +732,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ないか</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>是不是怎么….样</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>“否定+か”不再是否定，而是不确定的推测</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -741,17 +749,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ご存じでしょうか</t>
+          <t>本物そっくりに</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>您知道吗？（敬语）</t>
+          <t>和真的一模一样地</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ごぞんじでしょうか</t>
+          <t>ほんものそっくりに</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -762,40 +770,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>場合には</t>
+          <t>よう</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>在...的情况下</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ばあいには</t>
-        </is>
-      </c>
+          <t>(1)主观推测(2)比喻(3)示例</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>本物そっくりに</t>
+          <t>ものを</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>和真的一模一样地</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ほんものそっくりに</t>
-        </is>
-      </c>
+          <t>明明...却...（表不满、遗憾）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -804,12 +804,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>けっこう</t>
+          <t>Ｖる+うえで</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>相当，很；足够</t>
+          <t>在…方面，在…时</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -817,37 +817,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>点には</t>
+          <t>少しも + 否定</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>在...这一点上</t>
+          <t>一点也（不）...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>てんには</t>
+          <t>すこしも + ひてい</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>だけです</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>只是...而已</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -859,12 +859,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(V)おうとする</t>
+          <t>Ｖた＋うえで</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>在…之后，在…基础上</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -876,19 +876,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>介護</t>
+          <t>らしく</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>护理，照顾</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>かいご</t>
-        </is>
-      </c>
+          <t>らしい的中顿，而不是“らしくて”</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -897,16 +893,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>らしく</t>
+          <t>ところから</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>らしい的中顿，而不是“らしくて”</t>
+          <t>因为</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>同“ことから”“ことで”</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -914,15 +914,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ｖた＋うえで</t>
+          <t>楽しむ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>在…之后，在…基础上</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>享受</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>たのしむ</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -931,12 +935,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ｖる+うえで</t>
+          <t>エビ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>在…方面，在…时</t>
+          <t>虾</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -948,24 +952,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>少しも + 否定</t>
+          <t>うちに</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>一点也（不）...</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>すこしも + ひてい</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>没有不加否定的情况</t>
-        </is>
-      </c>
+          <t>在...期间；趁着...</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -973,20 +969,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>楽しむ</t>
+          <t>てばかり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>享受</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>たのしむ</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>净是...，光是...</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>“たばかり”刚…</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -994,12 +990,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>だけです</t>
+          <t>てもかまいません</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>只是...而已</t>
+          <t>...也没关系</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1011,12 +1007,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>エビ</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>虾</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1028,15 +1024,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>〜てしまう</t>
+          <t>介護</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>（动作）完成；（表示遗憾）</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>护理，照顾</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>かいご</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1066,15 +1066,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ものを</t>
+          <t>分野</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>明明...却...（表不满、遗憾）</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>领域，范围</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ぶんや</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1083,12 +1087,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>ようこそ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>欢迎</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1100,17 +1104,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>分野</t>
+          <t>ざるを得ない</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>领域，范围</t>
+          <t>不得不...</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ぶんや</t>
+          <t>ざるをえない</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1121,12 +1125,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ようこそ</t>
+          <t>にすぎない</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>欢迎</t>
+          <t>只不过是...</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1138,19 +1142,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ざるを得ない</t>
+          <t>Vる+つもり</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>不得不...</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ざるをえない</t>
-        </is>
-      </c>
+          <t>打算...</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1159,88 +1159,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>にすぎない</t>
+          <t>〜てしまう</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>只不过是...</t>
+          <t>（动作）完成；（表示遗憾）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>0</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Vる+つもり</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>打算...</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>てばかり</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>净是...，光是...</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>“たばかり”刚…</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>0</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>てもかまいません</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>...也没关系</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>うちに</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>在...期间；趁着...</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GRAMMAR/5_20_12.xlsx
+++ b/GRAMMAR/5_20_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -463,10 +463,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -480,6 +485,11 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,23 +507,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>お＋连用＋ました</t>
+          <t>たっけ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>自谦</t>
+          <t>（对于记不清的事进行确认）是…来着</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -521,16 +541,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ようこそ</t>
+          <t>お＋连用＋ました</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>欢迎</t>
+          <t>自谦</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -538,18 +563,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>なんて</t>
+          <t>ようこそ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(1)...之类的（表轻视或惊讶）(2)竟然</t>
+          <t>欢迎</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>“なんて～だろう”多么…啊</t>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -559,33 +585,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>たっけ</t>
+          <t>なんて</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>（对于记不清的事进行确认）是…来着</t>
+          <t>(1)...之类的（表轻视或惊讶）(2)竟然</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>“なんて～だろう”多么…啊</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>たことのある</t>
+          <t>N+のうえで(は)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>有过...经验的</t>
+          <t>根据…来看</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -593,16 +633,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N+のうえで(は)</t>
+          <t>たことのある</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>根据…来看</t>
+          <t>有过...经验的</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -620,6 +665,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -637,10 +687,15 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -654,6 +709,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -675,6 +735,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -696,6 +761,11 @@
           <t>同“ことから”“ことで”</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -713,6 +783,11 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -734,6 +809,11 @@
           <t>“否定+か”不再是否定，而是不确定的推测</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -755,6 +835,11 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -776,6 +861,11 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -797,6 +887,11 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -814,6 +909,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -835,6 +935,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -852,6 +957,11 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -869,6 +979,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -890,6 +1005,11 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -907,6 +1027,11 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -924,6 +1049,11 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -941,6 +1071,11 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -966,6 +1101,11 @@
           <t>没有不加否定的情况</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -987,6 +1127,11 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1004,6 +1149,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1021,6 +1171,11 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1038,6 +1193,11 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1059,6 +1219,11 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1076,6 +1241,11 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1093,6 +1263,11 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1114,6 +1289,11 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1131,6 +1311,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1152,6 +1337,11 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1169,6 +1359,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1186,6 +1381,11 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1207,6 +1407,11 @@
           <t>“たばかり”刚…</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1224,6 +1429,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1241,6 +1451,11 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
